--- a/Sipri_Analysis.xlsx
+++ b/Sipri_Analysis.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Riky\Desktop\Progetto SIPRI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CAF5429-086E-41CB-92FE-E8A5AC533672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FD6C21-808E-4395-828A-3308763DB95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="3270" yWindow="2985" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3615" yWindow="3330" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
-    <sheet name="Pivots" sheetId="5" r:id="rId2"/>
-    <sheet name="Clean_Data" sheetId="4" r:id="rId3"/>
-    <sheet name="Raw_Data" sheetId="2" r:id="rId4"/>
-    <sheet name="Countries_Registry" sheetId="3" r:id="rId5"/>
+    <sheet name="Pivots" sheetId="5" r:id="rId1"/>
+    <sheet name="Clean_Data" sheetId="4" r:id="rId2"/>
+    <sheet name="Raw_Data" sheetId="2" r:id="rId3"/>
+    <sheet name="Countries_Registry" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="70">
   <si>
     <t>Russia</t>
   </si>
@@ -111,9 +111,6 @@
     <t>United States</t>
   </si>
   <si>
-    <t>Increasing</t>
-  </si>
-  <si>
     <t>China</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
     <t>Ukraine</t>
   </si>
   <si>
-    <t>Decreasing</t>
-  </si>
-  <si>
     <t>France</t>
   </si>
   <si>
@@ -228,39 +222,6 @@
     <t>Southeast Asia</t>
   </si>
   <si>
-    <t>PORTFOLIO PROJECT – Global Military Spending Analysis (source: SIPRI)</t>
-  </si>
-  <si>
-    <t>This file contains:</t>
-  </si>
-  <si>
-    <t>• Sheet "Raw_Data": the dataset to clean and analyze. Contains INTENTIONALLY INSERTED errors.</t>
-  </si>
-  <si>
-    <t>• Sheet "Countries_Registry": clean support table for VLOOKUP (region, NATO, continent).</t>
-  </si>
-  <si>
-    <t>HOW TO WORK:</t>
-  </si>
-  <si>
-    <t>1. NEVER modify Raw_Data: make a copy immediately (right-click on the tab &gt; Move or Copy &gt; Create a copy) and rename it "Clean_Data". Always work on the copy.</t>
-  </si>
-  <si>
-    <t>2. Follow the PDF guide modules, one at a time.</t>
-  </si>
-  <si>
-    <t>3. After each module, take a screenshot of the result and write the corresponding section of the README.</t>
-  </si>
-  <si>
-    <t>DATA NOTE: values are rounded and derived from the SIPRI Military Expenditure Database (2025 release, 2024 data).</t>
-  </si>
-  <si>
-    <t>Before publishing the portfolio, download official data from sipri.org and verify/update the numbers: it's part of the exercise.</t>
-  </si>
-  <si>
-    <t>Spending in billions of current US dollars. "% GDP" = military spending as a ratio of GDP.</t>
-  </si>
-  <si>
     <t>NATO Countries:</t>
   </si>
   <si>
@@ -276,27 +237,12 @@
     <t>Military Effort</t>
   </si>
   <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
     <t>Index</t>
   </si>
   <si>
-    <t>Etichette di riga</t>
-  </si>
-  <si>
     <t>Totale complessivo</t>
   </si>
   <si>
-    <t>Conteggio di Country</t>
-  </si>
-  <si>
     <t>Countries</t>
   </si>
   <si>
@@ -304,9 +250,6 @@
   </si>
   <si>
     <t>Average of % GDP 2024</t>
-  </si>
-  <si>
-    <t>Etichette di colonna</t>
   </si>
 </sst>
 </file>
@@ -317,22 +260,13 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -511,43 +445,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -794,7 +723,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[progetto_sipri.xlsx]Pivots!PivotTable1</c:name>
+    <c:name>[Sipri_Analysis.xlsx]Pivots!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -2333,81 +2262,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{92793B64-599E-472C-B489-5643E4353F26}" name="Tabella pivot3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="F11:I16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Conteggio di Country" fld="0" subtotal="count" baseField="5" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9710724-C58F-4BA5-AC33-AFE50710E33B}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="NATO Membership">
   <location ref="F3:I6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -2474,7 +2328,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEC713C8-90E2-49DD-B00F-0C525C20B7A8}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
@@ -2899,85 +2753,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="120" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFDA25F-2F58-4CC3-9DE8-C91EFF6C95ED}">
-  <dimension ref="A3:I16"/>
+  <dimension ref="A3:I14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2990,28 +2767,28 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
-        <v>48</v>
+      <c r="A3" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="24" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="H3" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>1026.3</v>
@@ -3022,7 +2799,7 @@
       <c r="G4">
         <v>1003.3</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="25">
         <v>5.1000000000000005</v>
       </c>
       <c r="I4">
@@ -3031,18 +2808,18 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B5">
         <v>433.40000000000003</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>1457.7</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="25">
         <v>2.2066666666666661</v>
       </c>
       <c r="I5">
@@ -3051,18 +2828,18 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>375.2</v>
       </c>
       <c r="F6" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>2461.0000000000005</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="25">
         <v>3.7437500000000004</v>
       </c>
       <c r="I6">
@@ -3071,7 +2848,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <v>251.7</v>
@@ -3079,7 +2856,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B8">
         <v>151.80000000000001</v>
@@ -3087,7 +2864,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B9">
         <v>96.3</v>
@@ -3095,7 +2872,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B10">
         <v>45.9</v>
@@ -3108,105 +2885,38 @@
       <c r="B11">
         <v>33.799999999999997</v>
       </c>
-      <c r="F11" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>88</v>
-      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B12">
         <v>24.799999999999997</v>
       </c>
-      <c r="F12" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" t="s">
-        <v>83</v>
-      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B13">
         <v>21.8</v>
       </c>
-      <c r="F13" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
-      <c r="I13">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B14">
         <v>2461</v>
       </c>
-      <c r="F14" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14">
-        <v>3</v>
-      </c>
-      <c r="H14">
-        <v>15</v>
-      </c>
-      <c r="I14">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F15" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15">
-        <v>10</v>
-      </c>
-      <c r="I15">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F16" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-      <c r="H16">
-        <v>28</v>
-      </c>
-      <c r="I16">
-        <v>33</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF75FCB-253F-474B-BAF6-37F23D06B1E8}">
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3217,58 +2927,58 @@
     <col min="4" max="4" width="17.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.140625" customWidth="1"/>
     <col min="6" max="6" width="23.85546875" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="20" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" style="18" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
     <col min="11" max="11" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" s="21" t="s">
+      <c r="F1" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="21" t="s">
-        <v>49</v>
+      <c r="K1" s="19" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="3">
         <v>916</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="3">
         <v>997</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="7">
         <v>3.4</v>
       </c>
       <c r="E2" t="str">
@@ -3279,7 +2989,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>High</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="18">
         <v>8.8427947598253301E-2</v>
       </c>
       <c r="H2" t="str">
@@ -3300,16 +3010,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="5">
+      <c r="A3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="3">
         <v>296</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>314</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="7">
         <v>1.7</v>
       </c>
       <c r="E3" t="str">
@@ -3320,7 +3030,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>High</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="18">
         <v>6.08108108108108E-2</v>
       </c>
       <c r="H3" t="str">
@@ -3341,16 +3051,16 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>109</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>149</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="7">
         <v>7.1</v>
       </c>
       <c r="E4" t="str">
@@ -3361,7 +3071,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>High</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="18">
         <v>0.36697247706421998</v>
       </c>
       <c r="H4" t="str">
@@ -3382,16 +3092,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="5">
+      <c r="A5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="3">
         <v>66.8</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="3">
         <v>88.5</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="7">
         <v>1.9</v>
       </c>
       <c r="E5" t="str">
@@ -3402,7 +3112,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="18">
         <v>0.32485029940119797</v>
       </c>
       <c r="H5" t="str">
@@ -3423,16 +3133,16 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>83.6</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3">
         <v>86.1</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="7">
         <v>2.2999999999999998</v>
       </c>
       <c r="E6" t="str">
@@ -3443,7 +3153,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="18">
         <v>2.9904306220095701E-2</v>
       </c>
       <c r="H6" t="str">
@@ -3464,16 +3174,16 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3">
         <v>74.900000000000006</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="3">
         <v>81.8</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <v>2.2999999999999998</v>
       </c>
       <c r="E7" t="str">
@@ -3484,7 +3194,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="18">
         <v>9.2122830440587306E-2</v>
       </c>
       <c r="H7" t="str">
@@ -3505,16 +3215,16 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="5">
+      <c r="A8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3">
         <v>75.8</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="3">
         <v>80.3</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="7">
         <v>7.3</v>
       </c>
       <c r="E8" t="str">
@@ -3525,7 +3235,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="18">
         <v>5.9366754617414301E-2</v>
       </c>
       <c r="H8" t="str">
@@ -3546,16 +3256,16 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="5">
+      <c r="A9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="3">
         <v>64.8</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="3">
         <v>64.7</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="7">
         <v>34.5</v>
       </c>
       <c r="E9" t="str">
@@ -3566,7 +3276,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="18">
         <v>-1.54320987654312E-3</v>
       </c>
       <c r="H9" t="str">
@@ -3587,16 +3297,16 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="A10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="3">
         <v>61.3</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="3">
         <v>64.7</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="7">
         <v>2.1</v>
       </c>
       <c r="E10" t="str">
@@ -3607,7 +3317,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="18">
         <v>5.5464926590538401E-2</v>
       </c>
       <c r="H10" t="str">
@@ -3628,16 +3338,16 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="5">
+      <c r="A11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3">
         <v>50.2</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="3">
         <v>55.3</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="7">
         <v>1.4</v>
       </c>
       <c r="E11" t="str">
@@ -3648,7 +3358,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="18">
         <v>0.101593625498008</v>
       </c>
       <c r="H11" t="str">
@@ -3669,16 +3379,16 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="5">
+      <c r="A12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="3">
         <v>47.9</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="3">
         <v>47.6</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="7">
         <v>2.6</v>
       </c>
       <c r="E12" t="str">
@@ -3689,7 +3399,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="18">
         <v>-6.2630480167014E-3</v>
       </c>
       <c r="H12" t="str">
@@ -3710,16 +3420,16 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="5">
+      <c r="A13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="3">
         <v>27.5</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="3">
         <v>46.5</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="7">
         <v>8.8000000000000007</v>
       </c>
       <c r="E13" t="str">
@@ -3730,7 +3440,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="18">
         <v>0.69090909090909103</v>
       </c>
       <c r="H13" t="str">
@@ -3751,16 +3461,16 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="5">
+      <c r="A14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="3">
         <v>31.6</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="3">
         <v>38</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="7">
         <v>4.2</v>
       </c>
       <c r="E14" t="str">
@@ -3771,7 +3481,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="18">
         <v>0.20253164556962</v>
       </c>
       <c r="H14" t="str">
@@ -3792,16 +3502,16 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="5">
+      <c r="A15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3">
         <v>35.5</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="3">
         <v>38</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="7">
         <v>1.6</v>
       </c>
       <c r="E15" t="str">
@@ -3812,7 +3522,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="18">
         <v>7.0422535211267595E-2</v>
       </c>
       <c r="H15" t="str">
@@ -3833,16 +3543,16 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="3">
         <v>32.299999999999997</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="3">
         <v>33.799999999999997</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="7">
         <v>1.9</v>
       </c>
       <c r="E16" t="str">
@@ -3853,7 +3563,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="18">
         <v>4.6439628482972103E-2</v>
       </c>
       <c r="H16" t="str">
@@ -3874,16 +3584,16 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="3">
         <v>27.2</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="3">
         <v>29.3</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="7">
         <v>1.3</v>
       </c>
       <c r="E17" t="str">
@@ -3894,7 +3604,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="18">
         <v>7.7205882352941194E-2</v>
       </c>
       <c r="H17" t="str">
@@ -3915,16 +3625,16 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="5">
+      <c r="A18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="3">
         <v>15.8</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="3">
         <v>25</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="8">
         <v>1.9</v>
       </c>
       <c r="E18" t="str">
@@ -3935,7 +3645,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="18">
         <v>0.582278481012658</v>
       </c>
       <c r="H18" t="str">
@@ -3956,16 +3666,16 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="5">
+      <c r="A19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="3">
         <v>23.7</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="3">
         <v>24.5</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="7">
         <v>1.5</v>
       </c>
       <c r="E19" t="str">
@@ -3976,7 +3686,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="18">
         <v>3.37552742616034E-2</v>
       </c>
       <c r="H19" t="str">
@@ -3997,16 +3707,16 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5">
+      <c r="A20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="3">
         <v>22.9</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="3">
         <v>23.4</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="7">
         <v>1.1000000000000001</v>
       </c>
       <c r="E20" t="str">
@@ -4017,7 +3727,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="18">
         <v>2.1834061135371199E-2</v>
       </c>
       <c r="H20" t="str">
@@ -4038,16 +3748,16 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="3">
         <v>21.8</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="7">
         <v>8</v>
       </c>
       <c r="E21" t="str">
@@ -4076,16 +3786,16 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3">
         <v>16.600000000000001</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="3">
         <v>21.5</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="7">
         <v>1.9</v>
       </c>
       <c r="E22" t="str">
@@ -4096,7 +3806,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="18">
         <v>0.29518072289156599</v>
       </c>
       <c r="H22" t="str">
@@ -4117,16 +3827,16 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="3">
         <v>16.600000000000001</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="3">
         <v>16.5</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="9" t="s">
         <v>6</v>
       </c>
       <c r="E23" t="str">
@@ -4137,7 +3847,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="18">
         <v>-6.0240963855422497E-3</v>
       </c>
       <c r="H23" t="str">
@@ -4158,16 +3868,16 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="3">
         <v>13.7</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="3">
         <v>14.2</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="7">
         <v>2.8</v>
       </c>
       <c r="E24" t="str">
@@ -4178,7 +3888,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="18">
         <v>3.6496350364963501E-2</v>
       </c>
       <c r="H24" t="str">
@@ -4199,16 +3909,16 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="3">
         <v>11.8</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="3">
         <v>12.5</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="7">
         <v>0.6</v>
       </c>
       <c r="E25" t="str">
@@ -4219,7 +3929,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="18">
         <v>5.9322033898305003E-2</v>
       </c>
       <c r="H25" t="str">
@@ -4240,16 +3950,16 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="3">
         <v>8.8000000000000007</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="3">
         <v>12</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="7">
         <v>2</v>
       </c>
       <c r="E26" t="str">
@@ -4260,7 +3970,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="18">
         <v>0.36363636363636398</v>
       </c>
       <c r="H26" t="str">
@@ -4281,16 +3991,16 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="5">
+      <c r="A27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3">
         <v>8.6999999999999993</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="3">
         <v>10.9</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="7">
         <v>2.2000000000000002</v>
       </c>
       <c r="E27" t="str">
@@ -4301,7 +4011,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="18">
         <v>0.252873563218391</v>
       </c>
       <c r="H27" t="str">
@@ -4322,16 +4032,16 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="3">
         <v>9.5</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="3">
         <v>10.6</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="7">
         <v>0.8</v>
       </c>
       <c r="E28" t="str">
@@ -4342,7 +4052,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="18">
         <v>0.11578947368421</v>
       </c>
       <c r="H28" t="str">
@@ -4363,16 +4073,16 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="3">
         <v>8.5</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="3">
         <v>10.199999999999999</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="7">
         <v>2.7</v>
       </c>
       <c r="E29" t="str">
@@ -4383,7 +4093,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="18">
         <v>0.2</v>
       </c>
       <c r="H29" t="str">
@@ -4404,16 +4114,16 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="3">
         <v>8.1</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="3">
         <v>10</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="7">
         <v>2.4</v>
       </c>
       <c r="E30" t="str">
@@ -4424,7 +4134,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="18">
         <v>0.234567901234568</v>
       </c>
       <c r="H30" t="str">
@@ -4445,16 +4155,16 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="3">
         <v>10.7</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="3">
         <v>10</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="7">
         <v>2.4</v>
       </c>
       <c r="E31" t="str">
@@ -4465,7 +4175,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="18">
         <v>-6.5420560747663503E-2</v>
       </c>
       <c r="H31" t="str">
@@ -4486,16 +4196,16 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5">
+      <c r="A32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="3">
         <v>7.7</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="3">
         <v>8.5</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="7">
         <v>1.3</v>
       </c>
       <c r="E32" t="str">
@@ -4506,7 +4216,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="18">
         <v>0.103896103896104</v>
       </c>
       <c r="H32" t="str">
@@ -4527,16 +4237,16 @@
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="5">
+      <c r="A33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="3">
         <v>7.7</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="3">
         <v>8</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="7">
         <v>3.1</v>
       </c>
       <c r="E33" t="str">
@@ -4547,7 +4257,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="18">
         <v>3.8961038961038898E-2</v>
       </c>
       <c r="H33" t="str">
@@ -4568,16 +4278,16 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="16">
+      <c r="A34" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="14">
         <v>6.3</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="14">
         <v>6.8</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="15">
         <v>0.7</v>
       </c>
       <c r="E34" t="str">
@@ -4588,7 +4298,7 @@
         <f>IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=100,"High",IF(SpendTable[[#This Row],[Spending 2024 (bn $)]]&gt;=30,"Medium","Low"))</f>
         <v>Low</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="18">
         <v>7.9365079365079402E-2</v>
       </c>
       <c r="H34" t="str">
@@ -4609,27 +4319,27 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="23">
+      <c r="A37" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="21">
         <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="24">
+      <c r="A38" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="22">
         <v>0.69</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="B39" s="25" t="s">
-        <v>33</v>
+      <c r="A39" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -4640,7 +4350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4650,520 +4360,520 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="3">
         <v>916</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="3">
         <v>997</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="3">
         <v>3.4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="3">
+        <v>296</v>
+      </c>
+      <c r="C3" s="2">
+        <v>314</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3">
+        <v>109</v>
+      </c>
+      <c r="C4" s="3">
+        <v>149</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="5">
-        <v>296</v>
-      </c>
-      <c r="C3" s="4">
-        <v>314</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="5">
-        <v>109</v>
-      </c>
-      <c r="C4" s="5">
-        <v>149</v>
-      </c>
-      <c r="D4" s="5">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="3">
+        <v>66.8</v>
+      </c>
+      <c r="C5" s="3">
+        <v>88.5</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3">
+        <v>83.6</v>
+      </c>
+      <c r="C6" s="3">
+        <v>86.1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="5">
-        <v>66.8</v>
-      </c>
-      <c r="C5" s="5">
-        <v>88.5</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="B7" s="3">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="C7" s="3">
+        <v>81.8</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3">
+        <v>75.8</v>
+      </c>
+      <c r="C8" s="3">
+        <v>80.3</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="3">
+        <v>64.8</v>
+      </c>
+      <c r="C9" s="3">
+        <v>64.7</v>
+      </c>
+      <c r="D9" s="3">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="3">
+        <v>61.3</v>
+      </c>
+      <c r="C10" s="3">
+        <v>64.7</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="3">
+        <v>61.3</v>
+      </c>
+      <c r="C11" s="3">
+        <v>64.7</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="3">
+        <v>50.2</v>
+      </c>
+      <c r="C12" s="3">
+        <v>55.3</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="3">
+        <v>47.9</v>
+      </c>
+      <c r="C13" s="3">
+        <v>47.6</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46.5</v>
+      </c>
+      <c r="D14" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="3">
+        <v>31.6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>38</v>
+      </c>
+      <c r="D15" s="3">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="3">
+        <v>31.6</v>
+      </c>
+      <c r="C16" s="3">
+        <v>38</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="3">
+        <v>35.5</v>
+      </c>
+      <c r="C17" s="3">
+        <v>38</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="3">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="C18" s="3">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D18" s="3">
         <v>1.9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="5">
-        <v>83.6</v>
-      </c>
-      <c r="C6" s="5">
-        <v>86.1</v>
-      </c>
-      <c r="D6" s="5">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="5">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="C7" s="5">
-        <v>81.8</v>
-      </c>
-      <c r="D7" s="5">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="5">
-        <v>75.8</v>
-      </c>
-      <c r="C8" s="5">
-        <v>80.3</v>
-      </c>
-      <c r="D8" s="5">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="5">
-        <v>64.8</v>
-      </c>
-      <c r="C9" s="5">
-        <v>64.7</v>
-      </c>
-      <c r="D9" s="5">
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="5">
-        <v>61.3</v>
-      </c>
-      <c r="C10" s="5">
-        <v>64.7</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="5">
-        <v>61.3</v>
-      </c>
-      <c r="C11" s="5">
-        <v>64.7</v>
-      </c>
-      <c r="D11" s="5">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="5">
-        <v>50.2</v>
-      </c>
-      <c r="C12" s="5">
-        <v>55.3</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="5">
-        <v>47.9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>47.6</v>
-      </c>
-      <c r="D13" s="5">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="5">
-        <v>27.5</v>
-      </c>
-      <c r="C14" s="5">
-        <v>46.5</v>
-      </c>
-      <c r="D14" s="5">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="3">
+        <v>27.2</v>
+      </c>
+      <c r="C19" s="3">
+        <v>29.3</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="3">
+        <v>15.8</v>
+      </c>
+      <c r="C20" s="3">
+        <v>25</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="3">
+        <v>23.7</v>
+      </c>
+      <c r="C21" s="3">
+        <v>24.5</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="C22" s="3">
+        <v>21.5</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="3">
+        <v>21.8</v>
+      </c>
+      <c r="D23" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="3">
+        <v>22.9</v>
+      </c>
+      <c r="C24" s="3">
+        <v>23.4</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="3">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="C25" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3">
+        <v>916</v>
+      </c>
+      <c r="C26" s="3">
+        <v>997</v>
+      </c>
+      <c r="D26" s="3">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="3">
+        <v>13.7</v>
+      </c>
+      <c r="C27" s="3">
+        <v>14.2</v>
+      </c>
+      <c r="D27" s="3">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3">
+        <v>11.8</v>
+      </c>
+      <c r="C28" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3">
         <v>8.8000000000000007</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="5">
-        <v>31.6</v>
-      </c>
-      <c r="C15" s="5">
-        <v>38</v>
-      </c>
-      <c r="D15" s="5">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="5">
-        <v>31.6</v>
-      </c>
-      <c r="C16" s="5">
-        <v>38</v>
-      </c>
-      <c r="D16" s="5">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="5">
-        <v>35.5</v>
-      </c>
-      <c r="C17" s="5">
-        <v>38</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="C29" s="3">
+        <v>12</v>
+      </c>
+      <c r="D29" s="3">
         <v>2</v>
       </c>
-      <c r="B18" s="5">
-        <v>32.299999999999997</v>
-      </c>
-      <c r="C18" s="5">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="5">
-        <v>27.2</v>
-      </c>
-      <c r="C19" s="5">
-        <v>29.3</v>
-      </c>
-      <c r="D19" s="5">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="C30" s="3">
+        <v>10.9</v>
+      </c>
+      <c r="D30" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="C31" s="3">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="C32" s="3">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="C33" s="3">
+        <v>10.6</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="3">
+        <v>10.7</v>
+      </c>
+      <c r="C34" s="3">
+        <v>10</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="C35" s="3">
+        <v>8</v>
+      </c>
+      <c r="D35" s="3">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="C36" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="D36" s="3">
         <v>1.3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>25</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="5">
-        <v>23.7</v>
-      </c>
-      <c r="C21" s="5">
-        <v>24.5</v>
-      </c>
-      <c r="D21" s="5">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="5">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="C22" s="5">
-        <v>21.5</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="5">
-        <v>21.8</v>
-      </c>
-      <c r="D23" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5">
-        <v>22.9</v>
-      </c>
-      <c r="C24" s="5">
-        <v>23.4</v>
-      </c>
-      <c r="D24" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="5">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="C25" s="5">
-        <v>16.5</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="5">
-        <v>916</v>
-      </c>
-      <c r="C26" s="5">
-        <v>997</v>
-      </c>
-      <c r="D26" s="5">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="5">
-        <v>13.7</v>
-      </c>
-      <c r="C27" s="5">
-        <v>14.2</v>
-      </c>
-      <c r="D27" s="5">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5">
-        <v>11.8</v>
-      </c>
-      <c r="C28" s="5">
-        <v>12.5</v>
-      </c>
-      <c r="D28" s="5">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="C29" s="5">
-        <v>12</v>
-      </c>
-      <c r="D29" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="C30" s="5">
-        <v>10.9</v>
-      </c>
-      <c r="D30" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5">
-        <v>8.1</v>
-      </c>
-      <c r="C31" s="5">
-        <v>10</v>
-      </c>
-      <c r="D31" s="5">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="5">
-        <v>8.5</v>
-      </c>
-      <c r="C32" s="5">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D32" s="5">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="5">
-        <v>9.5</v>
-      </c>
-      <c r="C33" s="5">
-        <v>10.6</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="5">
-        <v>10.7</v>
-      </c>
-      <c r="C34" s="5">
-        <v>10</v>
-      </c>
-      <c r="D34" s="5">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="5">
-        <v>7.7</v>
-      </c>
-      <c r="C35" s="5">
-        <v>8</v>
-      </c>
-      <c r="D35" s="5">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="5">
-        <v>7.7</v>
-      </c>
-      <c r="C36" s="5">
-        <v>8.5</v>
-      </c>
-      <c r="D36" s="5">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="5">
+      <c r="B37" s="3">
         <v>6.3</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="3">
         <v>6.8</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="3">
         <v>0.7</v>
       </c>
     </row>
@@ -5172,7 +4882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5184,479 +4894,479 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="C29" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D29" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="4" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="D31" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="D34" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
